--- a/output/Data and Chart Outputs/nigeria_nnpc_gas_monthly.xlsx
+++ b/output/Data and Chart Outputs/nigeria_nnpc_gas_monthly.xlsx
@@ -1860,7 +1860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2091,16 +2091,16 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nnpc-limited-monthly-report-summary-july-2025</t>
+          <t>nnpc-limited-monthly-report-summary-august-2025</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://cms1977.nnpcgroup.com/uploads/NNPC_Limited_Monthly_Report_Summary_July_2025_2_b18aeb764b.pdf</t>
+          <t>https://cms1977.nnpcgroup.com/uploads/NNPC_Monthly_Report_August_2025_ver_4_889474532a.pdf</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2114,306 +2114,14 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>nnpc-limited-monthly-report-summary-august-2025</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>https://cms1977.nnpcgroup.com/uploads/NNPC_Monthly_Report_August_2025_ver_4_889474532a.pdf</t>
-        </is>
+        <v>46296</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>failed: ValueError: gas_production_mmscfd: 0 labels, 0 values</t>
+          <t>no page</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>45901</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>nnpc-limited-monthly-report-summary-september-2025</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>https://cms1977.nnpcgroup.com/uploads/NNPC_Limited_Monthly_Report_Summary_September_2025_c66b78eb4f.pdf</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>failed: ValueError: gas_production_mmscfd: 0 labels, 0 values</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>45931</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>nnpc-limited-monthly-report-summary-october-2025</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>https://cms1977.nnpcgroup.com/uploads/NNPC_Monthly_Report_OCTOBER_2025_V3_5eef1c59f6.pdf</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>failed: ValueError: gas_production_mmscfd: 0 labels, 0 values</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>45962</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>no page</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>45992</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>nnpc-limited-monthly-report-summary-december-2025</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://cms1977.nnpcgroup.com/uploads/NNPC_Monthly_Report_December_2025_ver_3_a65c21d6ac.pdf</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>failed: ValueError: gas_production_mmscfd: 0 labels, 0 values</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>nnpc-limited-monthly-report-summary-january-2026</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://cms1977.nnpcgroup.com/uploads/NNPC_Monthly_Report_January_2026_ver_5_1bfe95e677.pdf</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>46054</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>nnpc-limited-monthly-report-summary-february-2026</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>https://cms1977.nnpcgroup.com/uploads/NNPC_Monthly_Report_February_2026_8ba167f9d2.pdf</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
-        <v>46082</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>no page</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>nnpc-limited-monthly-report-summary-april-2026</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://cms1977.nnpcgroup.com/uploads/NNPC_Monthly_Report_April_2026_9e958e0848.pdf</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>nnpc-limited-monthly-report-summary-may-2026</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://cms1977.nnpcgroup.com/uploads/NNPC_Monthly_Report_May_2026_cdc0edb39f.pdf</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>nnpc-limited-monthly-report-summary-june-2026</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://cms1977.nnpcgroup.com/uploads/NNPC_Monthly_Report_June_2026_3922113ced.pdf</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
-        <v>46204</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>nnpc-limited-monthly-report-summary-july-2026</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://fde-nnpc-web-cms-prod-dwfrd0hraahrbhhg.a02.azurefd.net/uploads/NNPC_Ltd_Monthly_Report_for_July_2026_6f46510d5a.pdf</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="n">
-        <v>46235</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>nnpc-limited-monthly-report-summary-august-2026</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://fde-nnpc-web-cms-prod-dwfrd0hraahrbhhg.a02.azurefd.net/uploads/NNPC_Monthly_Report_for_August_2026_7f78b232ea.pdf</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>no page</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="n">
-        <v>46296</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>no page</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/nigeria_nnpc_gas_monthly.xlsx
+++ b/output/Data and Chart Outputs/nigeria_nnpc_gas_monthly.xlsx
@@ -1860,7 +1860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1970,7 +1970,7 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>45627</v>
+        <v>45658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>45658</v>
+        <v>46296</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1991,137 +1991,6 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>45689</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>no page</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>45717</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>no page</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>45748</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>nnpc-limited-monthly-report-summary-april-2025</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://cms1977.nnpcgroup.com/uploads/NNPC_Limited_Monthly_Report_Summary_April_2025_369c4d439f.pdf</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>failed: ValueError: gas_production_mmscfd: 0 labels, 4 values</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>nnpc-limited-monthly-report-summary-may-2025</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>https://cms1977.nnpcgroup.com/uploads/NNPC_Limited_Monthly_Report_Summary_May_2025_d100d752ad.pdf</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>failed: ValueError: gas_production_mmscfd: 0 labels, 0 values</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>45809</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>nnpc-limited-monthly-report-summary-june-2025</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>https://cms1977.nnpcgroup.com/uploads/NNPC_Limited_Monthly_Report_Summary_June_2025_2eec3acb2f.pdf</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>failed: ValueError: gas_production_mmscfd: 0 labels, 0 values</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>nnpc-limited-monthly-report-summary-august-2025</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>https://cms1977.nnpcgroup.com/uploads/NNPC_Monthly_Report_August_2025_ver_4_889474532a.pdf</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>failed: ValueError: gas_production_mmscfd: 0 labels, 0 values</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>46296</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>no page</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
         <v>0</v>
       </c>
     </row>
